--- a/grupos/4AEM - Estadisticos 20212.xlsx
+++ b/grupos/4AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -182,15 +182,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Torres Sánchez José Luis</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Torres Sánchez José Luis</t>
-  </si>
-  <si>
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
@@ -215,12 +215,48 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TLECUILE</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>HECTOR</t>
+  </si>
+  <si>
+    <t>IRVING URIEL</t>
+  </si>
+  <si>
+    <t>ANDRES NOEL</t>
+  </si>
+  <si>
     <t>ADELL</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
     <t>BUENO</t>
   </si>
   <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>COLOTL</t>
+  </si>
+  <si>
     <t>CORONA</t>
   </si>
   <si>
@@ -230,18 +266,18 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
     <t>NICIO</t>
   </si>
   <si>
@@ -254,45 +290,66 @@
     <t>ROMAN</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>TZANAHUA</t>
   </si>
   <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>XOCUA</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>TLECUILE</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>SOLIS</t>
   </si>
   <si>
-    <t>TEQUIHUATLE</t>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>JUAREZ</t>
   </si>
   <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
     <t>BALDERAS</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
+    <t>MIXCOHA</t>
   </si>
   <si>
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
@@ -305,24 +362,45 @@
     <t>YOPIHUA</t>
   </si>
   <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>BERISTAIN</t>
   </si>
   <si>
-    <t>HECTOR</t>
-  </si>
-  <si>
     <t>CRISTOPHER ALAIN</t>
   </si>
   <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
     <t>JORGE LUIS</t>
   </si>
   <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>ALMA RUBI</t>
+  </si>
+  <si>
     <t>JOSUE</t>
   </si>
   <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
@@ -332,18 +410,21 @@
     <t>LUIS ANGEL</t>
   </si>
   <si>
+    <t>ALEXIS MANUEL</t>
+  </si>
+  <si>
     <t>JUAN MANUEL</t>
   </si>
   <si>
-    <t>IRVING URIEL</t>
-  </si>
-  <si>
-    <t>ANDRES NOEL</t>
+    <t>DIEGO ADELFO</t>
   </si>
   <si>
     <t>OCTAVIO</t>
   </si>
   <si>
+    <t>JESUS HAZAEL</t>
+  </si>
+  <si>
     <t>JOSE JULIAN</t>
   </si>
   <si>
@@ -356,106 +437,25 @@
     <t>LUIS ALEJANDRO</t>
   </si>
   <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
     <t>JOSE MATEO</t>
   </si>
   <si>
     <t>OMAR</t>
   </si>
   <si>
+    <t>DIANA ARELI</t>
+  </si>
+  <si>
+    <t>ANGEL AMILCAR</t>
+  </si>
+  <si>
     <t>MARCOS URIEL</t>
   </si>
   <si>
     <t>CRISTAL</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>COLOTL</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>ALMA RUBI</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ALEXIS MANUEL</t>
-  </si>
-  <si>
-    <t>DIEGO ADELFO</t>
-  </si>
-  <si>
-    <t>JESUS HAZAEL</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>ANGEL AMILCAR</t>
   </si>
 </sst>
 </file>
@@ -960,7 +960,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -1023,7 +1023,7 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -1049,7 +1049,7 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -1112,7 +1112,7 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -1316,7 +1316,7 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -1379,7 +1379,7 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>6</v>
@@ -1672,7 +1672,7 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -1735,7 +1735,7 @@
         <v>5</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1761,7 +1761,7 @@
         <v>5</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -1824,7 +1824,7 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1939,7 +1939,7 @@
         <v>6</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>6</v>
@@ -2002,7 +2002,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -2028,7 +2028,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>6</v>
@@ -2091,7 +2091,7 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -2117,7 +2117,7 @@
         <v>6</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>6</v>
@@ -2180,7 +2180,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -2295,7 +2295,7 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -2358,7 +2358,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2384,7 +2384,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -2447,7 +2447,7 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2473,7 +2473,7 @@
         <v>6</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -2536,7 +2536,7 @@
         <v>6</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2651,7 +2651,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>6</v>
@@ -2714,7 +2714,7 @@
         <v>6</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -2740,7 +2740,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>6</v>
@@ -2803,7 +2803,7 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2829,7 +2829,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D25">
         <v>6</v>
@@ -2892,7 +2892,7 @@
         <v>6</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y25">
         <v>6</v>
@@ -2918,7 +2918,7 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D26">
         <v>6</v>
@@ -2981,7 +2981,7 @@
         <v>6</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -3007,7 +3007,7 @@
         <v>6</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -3070,7 +3070,7 @@
         <v>6</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -3363,7 +3363,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -3426,7 +3426,7 @@
         <v>6</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>6</v>
@@ -3541,7 +3541,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>6</v>
@@ -3604,7 +3604,7 @@
         <v>6</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y33">
         <v>6</v>
@@ -3719,7 +3719,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D35">
         <v>6</v>
@@ -3782,7 +3782,7 @@
         <v>6</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y35">
         <v>6</v>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -3862,30 +3862,30 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E2">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>65.63</v>
+      </c>
+      <c r="G2">
+        <v>34.38</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>40.63</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>7.7</v>
-      </c>
-      <c r="I2">
-        <v>19</v>
-      </c>
-      <c r="J2">
-        <v>59.38</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3894,30 +3894,30 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>65.63</v>
+        <v>75</v>
       </c>
       <c r="G3">
-        <v>34.38</v>
+        <v>21.88</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3926,25 +3926,25 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="G4">
-        <v>21.88</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4048,7 +4048,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8">
         <v>32</v>
@@ -4082,7 +4082,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4117,476 +4117,96 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920001</v>
+        <v>20330051920016</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920002</v>
+        <v>20330051920016</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920004</v>
+        <v>20330051920016</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920362</v>
+        <v>20330051920363</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920011</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920012</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920013</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920015</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920016</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920016</v>
-      </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920016</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920016</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920363</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920363</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920021</v>
-      </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920025</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" t="s">
-        <v>108</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920026</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" t="s">
-        <v>109</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920060</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" t="s">
-        <v>110</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920027</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" t="s">
-        <v>111</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920029</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" t="s">
-        <v>112</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920031</v>
-      </c>
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" t="s">
-        <v>94</v>
-      </c>
-      <c r="D23" t="s">
-        <v>113</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920035</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920037</v>
-      </c>
-      <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" t="s">
-        <v>115</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -4625,16 +4245,16 @@
         <v>20330051920016</v>
       </c>
       <c r="B2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
         <v>71</v>
       </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" t="s">
-        <v>105</v>
-      </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4645,13 +4265,13 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4659,16 +4279,16 @@
         <v>20330051920363</v>
       </c>
       <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" t="s">
         <v>72</v>
       </c>
-      <c r="C4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" t="s">
-        <v>106</v>
-      </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4676,282 +4296,282 @@
         <v>20330051920002</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920004</v>
+        <v>20330051920361</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920362</v>
+        <v>20330051920003</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920011</v>
+        <v>20330051920004</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920012</v>
+        <v>20330051920006</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920013</v>
+        <v>20330051920007</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920015</v>
+        <v>20330051920362</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
         <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920021</v>
+        <v>20330051920009</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920025</v>
+        <v>20330051920011</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920026</v>
+        <v>20330051920012</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920060</v>
+        <v>20330051920013</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920027</v>
+        <v>20330051920014</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920029</v>
+        <v>20330051920015</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920031</v>
+        <v>20330051920017</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920035</v>
+        <v>20330051920021</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920037</v>
+        <v>20330051920023</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920361</v>
+        <v>20330051920025</v>
       </c>
       <c r="B21" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
         <v>135</v>
@@ -4962,13 +4582,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920003</v>
+        <v>20330051920026</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s">
         <v>136</v>
@@ -4979,13 +4599,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920006</v>
+        <v>20330051920060</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
         <v>137</v>
@@ -4996,13 +4616,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920007</v>
+        <v>20330051920027</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D24" t="s">
         <v>138</v>
@@ -5013,13 +4633,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920009</v>
+        <v>20330051920028</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s">
         <v>139</v>
@@ -5030,13 +4650,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920014</v>
+        <v>20330051920029</v>
       </c>
       <c r="B26" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
         <v>140</v>
@@ -5047,13 +4667,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920017</v>
+        <v>20330051920031</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -5064,16 +4684,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920023</v>
+        <v>20330051920032</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5081,16 +4701,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920028</v>
+        <v>20330051920033</v>
       </c>
       <c r="B29" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5098,16 +4718,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920032</v>
+        <v>20330051920034</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5115,13 +4735,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920033</v>
+        <v>20330051920035</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D31" t="s">
         <v>144</v>
@@ -5132,16 +4752,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920034</v>
+        <v>20330051920036</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -5149,16 +4769,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920036</v>
+        <v>20330051920037</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="D33" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -5171,7 +4791,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5203,45 +4823,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920021</v>
+        <v>20330051920362</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920021</v>
+        <v>20330051920362</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5249,42 +4869,42 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920025</v>
+        <v>20330051920034</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>54</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920025</v>
+        <v>20330051920034</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>55</v>
@@ -5295,45 +4915,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920026</v>
+        <v>20330051920035</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920026</v>
+        <v>20330051920035</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5341,42 +4961,42 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920029</v>
+        <v>20330051920006</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920029</v>
+        <v>20330051920009</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>55</v>
@@ -5387,45 +5007,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920031</v>
+        <v>20330051920011</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920031</v>
+        <v>20330051920012</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5433,19 +5053,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920034</v>
+        <v>20330051920014</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
         <v>55</v>
@@ -5456,22 +5076,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920034</v>
+        <v>20330051920021</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" t="s">
         <v>133</v>
       </c>
-      <c r="D13" t="s">
-        <v>145</v>
-      </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5479,45 +5099,45 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920035</v>
+        <v>20330051920025</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
         <v>54</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920035</v>
+        <v>20330051920026</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -5525,45 +5145,45 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920037</v>
+        <v>20330051920029</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
         <v>54</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920037</v>
+        <v>20330051920031</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -5571,255 +5191,25 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920002</v>
+        <v>20330051920037</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
         <v>54</v>
       </c>
       <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920004</v>
-      </c>
-      <c r="B19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" t="s">
-        <v>99</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920006</v>
-      </c>
-      <c r="B20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C20" t="s">
-        <v>128</v>
-      </c>
-      <c r="D20" t="s">
-        <v>137</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920009</v>
-      </c>
-      <c r="B21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" t="s">
-        <v>123</v>
-      </c>
-      <c r="D21" t="s">
-        <v>139</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>56</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920011</v>
-      </c>
-      <c r="B22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" t="s">
-        <v>101</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920012</v>
-      </c>
-      <c r="B23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920013</v>
-      </c>
-      <c r="B24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920014</v>
-      </c>
-      <c r="B25" t="s">
-        <v>120</v>
-      </c>
-      <c r="C25" t="s">
-        <v>129</v>
-      </c>
-      <c r="D25" t="s">
-        <v>140</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>56</v>
-      </c>
-      <c r="G25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920015</v>
-      </c>
-      <c r="B26" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" t="s">
-        <v>104</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920060</v>
-      </c>
-      <c r="B27" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>54</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920027</v>
-      </c>
-      <c r="B28" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" t="s">
-        <v>92</v>
-      </c>
-      <c r="D28" t="s">
-        <v>111</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4AEM - Estadisticos 20212.xlsx
+++ b/grupos/4AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -182,19 +182,19 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Torres Sánchez José Luis</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Torres Sánchez José Luis</t>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
     <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
     <t>Medina Tolentino Elio</t>
@@ -987,7 +987,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1029,7 +1029,7 @@
         <v>7</v>
       </c>
       <c r="Z4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA4">
         <v>10</v>
@@ -1076,7 +1076,7 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1159,13 +1159,13 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1201,7 +1201,7 @@
         <v>6</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -1248,13 +1248,13 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1290,7 +1290,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1337,13 +1337,13 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1379,13 +1379,13 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>6</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA8">
         <v>8</v>
@@ -1426,13 +1426,13 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1468,13 +1468,13 @@
         <v>6</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>6</v>
       </c>
       <c r="Z9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA9">
         <v>7</v>
@@ -1515,13 +1515,13 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1557,13 +1557,13 @@
         <v>6</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>6</v>
       </c>
       <c r="Z10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA10">
         <v>7</v>
@@ -1604,13 +1604,13 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1646,7 +1646,7 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>6</v>
@@ -1699,7 +1699,7 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1788,7 +1788,7 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1871,13 +1871,13 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1960,13 +1960,13 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -2002,7 +2002,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -2049,13 +2049,13 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -2091,7 +2091,7 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -2138,13 +2138,13 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2186,7 +2186,7 @@
         <v>6</v>
       </c>
       <c r="Z17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA17">
         <v>8</v>
@@ -2233,7 +2233,7 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2316,13 +2316,13 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2358,7 +2358,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2405,13 +2405,13 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2447,7 +2447,7 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2494,13 +2494,13 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2536,13 +2536,13 @@
         <v>6</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>6</v>
       </c>
       <c r="Z21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA21">
         <v>7</v>
@@ -2583,13 +2583,13 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2625,13 +2625,13 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>6</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2678,7 +2678,7 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2767,7 +2767,7 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2809,7 +2809,7 @@
         <v>6</v>
       </c>
       <c r="Z24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>10</v>
@@ -2850,13 +2850,13 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2898,7 +2898,7 @@
         <v>6</v>
       </c>
       <c r="Z25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA25">
         <v>10</v>
@@ -2939,13 +2939,13 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2981,7 +2981,7 @@
         <v>6</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -3028,13 +3028,13 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -3070,13 +3070,13 @@
         <v>6</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>6</v>
       </c>
       <c r="Z27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA27">
         <v>9</v>
@@ -3117,13 +3117,13 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -3159,7 +3159,7 @@
         <v>6</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -3206,13 +3206,13 @@
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -3295,13 +3295,13 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3337,7 +3337,7 @@
         <v>6</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -3384,13 +3384,13 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3426,13 +3426,13 @@
         <v>6</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>6</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>10</v>
@@ -3473,13 +3473,13 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3515,13 +3515,13 @@
         <v>6</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>8</v>
       </c>
       <c r="Z32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA32">
         <v>7</v>
@@ -3562,13 +3562,13 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3604,7 +3604,7 @@
         <v>6</v>
       </c>
       <c r="X33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>6</v>
@@ -3651,13 +3651,13 @@
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3693,7 +3693,7 @@
         <v>6</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>6</v>
@@ -3746,7 +3746,7 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -3862,30 +3862,30 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>65.63</v>
+        <v>75</v>
       </c>
       <c r="G2">
-        <v>34.38</v>
+        <v>21.88</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3894,30 +3894,30 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3">
         <v>7</v>
       </c>
       <c r="F3">
-        <v>75</v>
+        <v>78.13</v>
       </c>
       <c r="G3">
         <v>21.88</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3938,7 +3938,7 @@
         <v>12.5</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3958,30 +3958,30 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>87.5</v>
+        <v>90.63</v>
       </c>
       <c r="G5">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>5.9</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -3990,25 +3990,25 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>90.63</v>
+        <v>96.88</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="H6">
         <v>7.5</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4048,7 +4048,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8">
         <v>32</v>
@@ -4126,7 +4126,7 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4146,7 +4146,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4166,7 +4166,7 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4186,7 +4186,7 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4206,7 +4206,7 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4791,7 +4791,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4838,7 +4838,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4861,7 +4861,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4869,19 +4869,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920034</v>
+        <v>20330051920006</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>54</v>
@@ -4892,22 +4892,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920034</v>
+        <v>20330051920009</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920035</v>
+        <v>20330051920014</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4938,19 +4938,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920035</v>
+        <v>20330051920021</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>54</v>
@@ -4961,19 +4961,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920006</v>
+        <v>20330051920025</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
         <v>55</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920009</v>
+        <v>20330051920034</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5007,22 +5007,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920011</v>
+        <v>20330051920035</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5030,185 +5030,24 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920012</v>
+        <v>20330051920037</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920014</v>
-      </c>
-      <c r="B12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" t="s">
-        <v>130</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920021</v>
-      </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" t="s">
-        <v>133</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920025</v>
-      </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" t="s">
-        <v>135</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920026</v>
-      </c>
-      <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" t="s">
-        <v>111</v>
-      </c>
-      <c r="D15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920029</v>
-      </c>
-      <c r="B16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" t="s">
-        <v>140</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920031</v>
-      </c>
-      <c r="B17" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" t="s">
-        <v>141</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920037</v>
-      </c>
-      <c r="B18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" t="s">
-        <v>145</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEM - Estadisticos 20212.xlsx
+++ b/grupos/4AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -182,24 +182,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -215,208 +215,208 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>BUENO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>COLOTL</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
     <t>TLECUILE</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
     <t>AMADOR</t>
   </si>
   <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
     <t>HECTOR</t>
   </si>
   <si>
+    <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>JORGE LUIS</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>ALMA RUBI</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>ALEXIS MANUEL</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL</t>
+  </si>
+  <si>
     <t>IRVING URIEL</t>
   </si>
   <si>
+    <t>DIEGO ADELFO</t>
+  </si>
+  <si>
     <t>ANDRES NOEL</t>
-  </si>
-  <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>BUENO</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>COLOTL</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ALAIN</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>JORGE LUIS</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>ALMA RUBI</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ALEXIS MANUEL</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL</t>
-  </si>
-  <si>
-    <t>DIEGO ADELFO</t>
   </si>
   <si>
     <t>OCTAVIO</t>
@@ -978,25 +978,25 @@
         <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1020,13 +1020,13 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X4">
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z4">
         <v>6</v>
@@ -1038,7 +1038,7 @@
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1064,28 +1064,28 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1112,22 +1112,22 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z5">
         <v>5</v>
       </c>
       <c r="AA5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC5">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1156,25 +1156,25 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1204,7 +1204,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z6">
         <v>10</v>
@@ -1245,25 +1245,25 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1293,7 +1293,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>10</v>
@@ -1305,7 +1305,7 @@
         <v>10</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1334,25 +1334,25 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1382,16 +1382,16 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z8">
         <v>9</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>8</v>
@@ -1423,25 +1423,25 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1471,19 +1471,19 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z9">
         <v>10</v>
       </c>
       <c r="AA9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1512,25 +1512,25 @@
         <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1560,16 +1560,16 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z10">
         <v>9</v>
       </c>
       <c r="AA10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC10">
         <v>7</v>
@@ -1601,25 +1601,25 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1649,7 +1649,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z11">
         <v>9</v>
@@ -1690,25 +1690,25 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1735,10 +1735,10 @@
         <v>5</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -1770,34 +1770,34 @@
         <v>5</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1833,13 +1833,13 @@
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC13">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1868,25 +1868,25 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
         <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1910,13 +1910,13 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z14">
         <v>10</v>
@@ -1925,7 +1925,7 @@
         <v>9</v>
       </c>
       <c r="AB14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>10</v>
@@ -1957,25 +1957,25 @@
         <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -2005,7 +2005,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z15">
         <v>10</v>
@@ -2017,7 +2017,7 @@
         <v>10</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2046,25 +2046,25 @@
         <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2094,7 +2094,7 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z16">
         <v>10</v>
@@ -2106,7 +2106,7 @@
         <v>10</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2135,25 +2135,25 @@
         <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2177,22 +2177,22 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z17">
         <v>8</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>8</v>
@@ -2224,25 +2224,25 @@
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2272,19 +2272,19 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z18">
         <v>7</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2313,25 +2313,25 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2399,28 +2399,28 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2450,19 +2450,19 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z20">
         <v>5</v>
       </c>
       <c r="AA20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC20">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2491,25 +2491,25 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2533,25 +2533,25 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X21">
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z21">
         <v>10</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2580,25 +2580,25 @@
         <v>7</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2622,13 +2622,13 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z22">
         <v>8</v>
@@ -2640,7 +2640,7 @@
         <v>10</v>
       </c>
       <c r="AC22">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2669,25 +2669,25 @@
         <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2711,22 +2711,22 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z23">
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -2758,25 +2758,25 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2803,10 +2803,10 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z24">
         <v>6</v>
@@ -2847,25 +2847,25 @@
         <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L25">
         <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2895,7 +2895,7 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z25">
         <v>8</v>
@@ -2907,7 +2907,7 @@
         <v>10</v>
       </c>
       <c r="AC25">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2936,25 +2936,25 @@
         <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
         <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2978,25 +2978,25 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z26">
         <v>9</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -3025,25 +3025,25 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3067,13 +3067,13 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z27">
         <v>6</v>
@@ -3082,10 +3082,10 @@
         <v>9</v>
       </c>
       <c r="AB27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3114,25 +3114,25 @@
         <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3156,25 +3156,25 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X28">
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z28">
         <v>9</v>
       </c>
       <c r="AA28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC28">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3203,25 +3203,25 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
         <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3251,16 +3251,16 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z29">
         <v>10</v>
       </c>
       <c r="AA29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC29">
         <v>10</v>
@@ -3292,25 +3292,25 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3340,16 +3340,16 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>8</v>
       </c>
       <c r="AA30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC30">
         <v>8</v>
@@ -3381,25 +3381,25 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
         <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3423,13 +3423,13 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z31">
         <v>7</v>
@@ -3441,7 +3441,7 @@
         <v>10</v>
       </c>
       <c r="AC31">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3470,25 +3470,25 @@
         <v>6</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
         <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
         <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3518,19 +3518,19 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z32">
         <v>6</v>
       </c>
       <c r="AA32">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC32">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3559,25 +3559,25 @@
         <v>7</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
         <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L33">
         <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3607,7 +3607,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z33">
         <v>5</v>
@@ -3648,25 +3648,25 @@
         <v>7</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
         <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3696,19 +3696,19 @@
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z34">
         <v>9</v>
       </c>
       <c r="AA34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC34">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3737,25 +3737,25 @@
         <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L35">
         <v>5</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3779,25 +3779,25 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z35">
         <v>5</v>
       </c>
       <c r="AA35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC35">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -3862,30 +3862,30 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>75</v>
+        <v>15.63</v>
       </c>
       <c r="G2">
-        <v>21.88</v>
+        <v>84.38</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3894,19 +3894,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>78.13</v>
+        <v>65.63</v>
       </c>
       <c r="G3">
-        <v>21.88</v>
+        <v>34.38</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3917,7 +3917,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3926,19 +3926,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>87.5</v>
+        <v>78.13</v>
       </c>
       <c r="G4">
-        <v>12.5</v>
+        <v>21.88</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3958,30 +3958,30 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>90.63</v>
+        <v>84.38</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>15.63</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -3990,19 +3990,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -4022,19 +4022,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4048,31 +4048,31 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C8">
         <v>32</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4082,7 +4082,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4107,106 +4107,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920016</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920016</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920016</v>
-      </c>
-      <c r="B5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920363</v>
-      </c>
-      <c r="B6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4242,64 +4142,64 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920016</v>
+        <v>20330051920001</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920001</v>
+        <v>20330051920002</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920363</v>
+        <v>20330051920361</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920002</v>
+        <v>20330051920003</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
         <v>119</v>
@@ -4310,13 +4210,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920361</v>
+        <v>20330051920004</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
         <v>120</v>
@@ -4327,13 +4227,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920003</v>
+        <v>20330051920006</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
         <v>121</v>
@@ -4344,13 +4244,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920004</v>
+        <v>20330051920007</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
         <v>122</v>
@@ -4361,13 +4261,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920006</v>
+        <v>20330051920362</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
         <v>123</v>
@@ -4378,13 +4278,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920007</v>
+        <v>20330051920009</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
         <v>124</v>
@@ -4395,10 +4295,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920362</v>
+        <v>20330051920011</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
         <v>87</v>
@@ -4412,13 +4312,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920009</v>
+        <v>20330051920012</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
         <v>126</v>
@@ -4429,13 +4329,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920011</v>
+        <v>20330051920013</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
         <v>127</v>
@@ -4446,13 +4346,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920012</v>
+        <v>20330051920014</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
         <v>128</v>
@@ -4463,13 +4363,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920013</v>
+        <v>20330051920015</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
         <v>129</v>
@@ -4480,13 +4380,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920014</v>
+        <v>20330051920016</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
         <v>130</v>
@@ -4497,13 +4397,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920015</v>
+        <v>20330051920017</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
         <v>131</v>
@@ -4514,13 +4414,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920017</v>
+        <v>20330051920363</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
         <v>132</v>
@@ -4534,10 +4434,10 @@
         <v>20330051920021</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
         <v>133</v>
@@ -4551,10 +4451,10 @@
         <v>20330051920023</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
         <v>134</v>
@@ -4568,10 +4468,10 @@
         <v>20330051920025</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
         <v>135</v>
@@ -4585,10 +4485,10 @@
         <v>20330051920026</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
         <v>136</v>
@@ -4602,10 +4502,10 @@
         <v>20330051920060</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
         <v>137</v>
@@ -4619,10 +4519,10 @@
         <v>20330051920027</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
         <v>138</v>
@@ -4636,10 +4536,10 @@
         <v>20330051920028</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
         <v>139</v>
@@ -4653,10 +4553,10 @@
         <v>20330051920029</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
         <v>140</v>
@@ -4670,10 +4570,10 @@
         <v>20330051920031</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4687,13 +4587,13 @@
         <v>20330051920032</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4704,10 +4604,10 @@
         <v>20330051920033</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
         <v>142</v>
@@ -4721,10 +4621,10 @@
         <v>20330051920034</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
         <v>143</v>
@@ -4738,10 +4638,10 @@
         <v>20330051920035</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D31" t="s">
         <v>144</v>
@@ -4755,13 +4655,13 @@
         <v>20330051920036</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -4772,10 +4672,10 @@
         <v>20330051920037</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -4791,7 +4691,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4823,22 +4723,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920362</v>
+        <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4846,22 +4746,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920362</v>
+        <v>20330051920002</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4869,22 +4769,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920006</v>
+        <v>20330051920013</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4892,19 +4792,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920009</v>
+        <v>20330051920013</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>54</v>
@@ -4915,22 +4815,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920014</v>
+        <v>20330051920021</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
         <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4941,16 +4841,16 @@
         <v>20330051920021</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
         <v>133</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>54</v>
@@ -4961,22 +4861,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920025</v>
+        <v>20330051920026</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4984,19 +4884,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920034</v>
+        <v>20330051920026</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
         <v>54</v>
@@ -5007,19 +4907,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920035</v>
+        <v>20330051920029</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
         <v>55</v>
@@ -5030,24 +4930,438 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920037</v>
+        <v>20330051920029</v>
       </c>
       <c r="B11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" t="s">
+        <v>140</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920035</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" t="s">
+        <v>144</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920035</v>
+      </c>
+      <c r="B13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920361</v>
+      </c>
+      <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920004</v>
+      </c>
+      <c r="B15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920006</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s">
         <v>98</v>
       </c>
-      <c r="C11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" t="s">
-        <v>145</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="D16" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920007</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920009</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920011</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920012</v>
+      </c>
+      <c r="B20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920014</v>
+      </c>
+      <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920017</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920023</v>
+      </c>
+      <c r="B23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920060</v>
+      </c>
+      <c r="B24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" t="s">
+        <v>137</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>54</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920027</v>
+      </c>
+      <c r="B25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D25" t="s">
+        <v>138</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>20330051920028</v>
+      </c>
+      <c r="B26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E26" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" t="s">
         <v>55</v>
       </c>
-      <c r="G11">
+      <c r="G26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920031</v>
+      </c>
+      <c r="B27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" t="s">
+        <v>141</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>54</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920032</v>
+      </c>
+      <c r="B28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" t="s">
+        <v>121</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920036</v>
+      </c>
+      <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" t="s">
+        <v>119</v>
+      </c>
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEM - Estadisticos 20212.xlsx
+++ b/grupos/4AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -182,16 +182,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
     <t>Torres Sánchez José Luis</t>
@@ -984,7 +984,7 @@
         <v>6</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -1002,13 +1002,13 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -1023,10 +1023,10 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z4">
         <v>6</v>
@@ -1073,7 +1073,7 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -1091,13 +1091,13 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -1112,13 +1112,13 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA5">
         <v>8</v>
@@ -1162,7 +1162,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -1180,13 +1180,13 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1204,7 +1204,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <v>10</v>
@@ -1251,7 +1251,7 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>9</v>
@@ -1269,13 +1269,13 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1293,7 +1293,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z7">
         <v>10</v>
@@ -1340,7 +1340,7 @@
         <v>8</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>8</v>
@@ -1358,13 +1358,13 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1382,7 +1382,7 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z8">
         <v>9</v>
@@ -1429,7 +1429,7 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1447,13 +1447,13 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1468,10 +1468,10 @@
         <v>6</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z9">
         <v>10</v>
@@ -1518,7 +1518,7 @@
         <v>9</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1530,19 +1530,19 @@
         <v>10</v>
       </c>
       <c r="O10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1560,7 +1560,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z10">
         <v>9</v>
@@ -1572,7 +1572,7 @@
         <v>8</v>
       </c>
       <c r="AC10">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1607,7 +1607,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>8</v>
@@ -1625,13 +1625,13 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1649,10 +1649,10 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>10</v>
@@ -1696,7 +1696,7 @@
         <v>5</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>5</v>
@@ -1714,13 +1714,13 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -1735,13 +1735,13 @@
         <v>5</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA12">
         <v>10</v>
@@ -1785,7 +1785,7 @@
         <v>6</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -1803,13 +1803,13 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -1824,13 +1824,13 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>8</v>
@@ -1874,7 +1874,7 @@
         <v>9</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -1892,13 +1892,13 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -1916,7 +1916,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z14">
         <v>10</v>
@@ -1963,7 +1963,7 @@
         <v>9</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>10</v>
@@ -1981,13 +1981,13 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -2002,10 +2002,10 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z15">
         <v>10</v>
@@ -2052,7 +2052,7 @@
         <v>9</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -2070,13 +2070,13 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -2091,10 +2091,10 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z16">
         <v>10</v>
@@ -2141,7 +2141,7 @@
         <v>6</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>7</v>
@@ -2159,13 +2159,13 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -2180,13 +2180,13 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>9</v>
@@ -2230,7 +2230,7 @@
         <v>7</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -2248,13 +2248,13 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2269,13 +2269,13 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>9</v>
@@ -2319,7 +2319,7 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -2337,13 +2337,13 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2358,10 +2358,10 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z19">
         <v>10</v>
@@ -2408,7 +2408,7 @@
         <v>9</v>
       </c>
       <c r="K20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>6</v>
@@ -2426,13 +2426,13 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2447,13 +2447,13 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA20">
         <v>9</v>
@@ -2497,7 +2497,7 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -2515,13 +2515,13 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -2539,10 +2539,10 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA21">
         <v>8</v>
@@ -2586,7 +2586,7 @@
         <v>9</v>
       </c>
       <c r="K22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>9</v>
@@ -2604,13 +2604,13 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -2628,7 +2628,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z22">
         <v>8</v>
@@ -2675,7 +2675,7 @@
         <v>6</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>5</v>
@@ -2693,13 +2693,13 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -2714,13 +2714,13 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>9</v>
@@ -2764,7 +2764,7 @@
         <v>5</v>
       </c>
       <c r="K24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>7</v>
@@ -2782,13 +2782,13 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
         <v>-1</v>
@@ -2806,7 +2806,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z24">
         <v>6</v>
@@ -2853,7 +2853,7 @@
         <v>6</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>8</v>
@@ -2871,13 +2871,13 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>-1</v>
@@ -2892,10 +2892,10 @@
         <v>6</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z25">
         <v>8</v>
@@ -2942,7 +2942,7 @@
         <v>10</v>
       </c>
       <c r="K26">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>8</v>
@@ -2960,13 +2960,13 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>-1</v>
@@ -2984,7 +2984,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z26">
         <v>9</v>
@@ -3031,7 +3031,7 @@
         <v>8</v>
       </c>
       <c r="K27">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>7</v>
@@ -3049,13 +3049,13 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
         <v>-1</v>
@@ -3073,7 +3073,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z27">
         <v>6</v>
@@ -3120,7 +3120,7 @@
         <v>9</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>9</v>
@@ -3138,13 +3138,13 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T28">
         <v>-1</v>
@@ -3159,13 +3159,13 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA28">
         <v>10</v>
@@ -3209,7 +3209,7 @@
         <v>9</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -3227,13 +3227,13 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>-1</v>
@@ -3251,7 +3251,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z29">
         <v>10</v>
@@ -3298,7 +3298,7 @@
         <v>9</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>7</v>
@@ -3316,13 +3316,13 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
         <v>-1</v>
@@ -3337,13 +3337,13 @@
         <v>6</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA30">
         <v>10</v>
@@ -3387,7 +3387,7 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>9</v>
@@ -3405,13 +3405,13 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>-1</v>
@@ -3429,10 +3429,10 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA31">
         <v>10</v>
@@ -3476,7 +3476,7 @@
         <v>9</v>
       </c>
       <c r="K32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>7</v>
@@ -3494,13 +3494,13 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T32">
         <v>-1</v>
@@ -3518,7 +3518,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z32">
         <v>6</v>
@@ -3565,7 +3565,7 @@
         <v>8</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>5</v>
@@ -3583,13 +3583,13 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
         <v>-1</v>
@@ -3607,10 +3607,10 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA33">
         <v>10</v>
@@ -3654,7 +3654,7 @@
         <v>9</v>
       </c>
       <c r="K34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>9</v>
@@ -3672,13 +3672,13 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>-1</v>
@@ -3696,7 +3696,7 @@
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z34">
         <v>9</v>
@@ -3743,7 +3743,7 @@
         <v>5</v>
       </c>
       <c r="K35">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -3761,13 +3761,13 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>-1</v>
@@ -3782,13 +3782,13 @@
         <v>5</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA35">
         <v>9</v>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -3862,19 +3862,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>15.63</v>
+        <v>65.63</v>
       </c>
       <c r="G2">
-        <v>84.38</v>
+        <v>34.38</v>
       </c>
       <c r="H2">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3885,7 +3885,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3894,19 +3894,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>65.63</v>
+        <v>96.88</v>
       </c>
       <c r="G3">
-        <v>34.38</v>
+        <v>3.13</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3917,7 +3917,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3926,19 +3926,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>21.88</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3958,19 +3958,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>15.63</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4034,7 +4034,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4691,7 +4691,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4723,22 +4723,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920002</v>
+        <v>20330051920001</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4758,7 +4758,7 @@
         <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
@@ -4769,22 +4769,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920013</v>
+        <v>20330051920362</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4804,7 +4804,7 @@
         <v>127</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>54</v>
@@ -4815,22 +4815,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920021</v>
+        <v>20330051920016</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4838,19 +4838,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920021</v>
+        <v>20330051920363</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
         <v>54</v>
@@ -4861,22 +4861,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920026</v>
+        <v>20330051920021</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4884,19 +4884,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920026</v>
+        <v>20330051920025</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>54</v>
@@ -4907,19 +4907,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920029</v>
+        <v>20330051920026</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>55</v>
@@ -4930,19 +4930,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920029</v>
+        <v>20330051920028</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
@@ -4953,19 +4953,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920035</v>
+        <v>20330051920029</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
         <v>54</v>
@@ -4976,392 +4976,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920035</v>
+        <v>20330051920037</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920361</v>
-      </c>
-      <c r="B14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920004</v>
-      </c>
-      <c r="B15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" t="s">
-        <v>120</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920006</v>
-      </c>
-      <c r="B16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16" t="s">
-        <v>121</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920007</v>
-      </c>
-      <c r="B17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" t="s">
-        <v>122</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920009</v>
-      </c>
-      <c r="B18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" t="s">
-        <v>88</v>
-      </c>
-      <c r="D18" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920011</v>
-      </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" t="s">
-        <v>125</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920012</v>
-      </c>
-      <c r="B20" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920014</v>
-      </c>
-      <c r="B21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" t="s">
-        <v>100</v>
-      </c>
-      <c r="D21" t="s">
-        <v>128</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920017</v>
-      </c>
-      <c r="B22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" t="s">
-        <v>131</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920023</v>
-      </c>
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" t="s">
-        <v>106</v>
-      </c>
-      <c r="D23" t="s">
-        <v>134</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920060</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920027</v>
-      </c>
-      <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" t="s">
-        <v>108</v>
-      </c>
-      <c r="D25" t="s">
-        <v>138</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>54</v>
-      </c>
-      <c r="G25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920028</v>
-      </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>55</v>
-      </c>
-      <c r="G26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920031</v>
-      </c>
-      <c r="B27" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" t="s">
-        <v>110</v>
-      </c>
-      <c r="D27" t="s">
-        <v>141</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>54</v>
-      </c>
-      <c r="G27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920032</v>
-      </c>
-      <c r="B28" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" t="s">
-        <v>121</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920036</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>114</v>
-      </c>
-      <c r="D29" t="s">
-        <v>119</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>54</v>
-      </c>
-      <c r="G29">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEM - Estadisticos 20212.xlsx
+++ b/grupos/4AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -999,34 +999,34 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>7</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z4">
         <v>6</v>
@@ -1088,25 +1088,25 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>8</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>5</v>
@@ -1177,25 +1177,25 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1266,25 +1266,25 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1355,25 +1355,25 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
         <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>10</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>6</v>
@@ -1391,10 +1391,10 @@
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1444,25 +1444,25 @@
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
         <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -1480,7 +1480,7 @@
         <v>8</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC9">
         <v>9</v>
@@ -1533,25 +1533,25 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>6</v>
@@ -1622,25 +1622,25 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
         <v>6</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>6</v>
@@ -1711,25 +1711,25 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>8</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1800,25 +1800,25 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>8</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1827,7 +1827,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>6</v>
@@ -1839,7 +1839,7 @@
         <v>9</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1889,25 +1889,25 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>10</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1925,7 +1925,7 @@
         <v>9</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC14">
         <v>10</v>
@@ -1978,25 +1978,25 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -2067,25 +2067,25 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>10</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -2156,25 +2156,25 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
         <v>6</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -2189,13 +2189,13 @@
         <v>7</v>
       </c>
       <c r="AA17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2245,25 +2245,25 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>10</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>6</v>
@@ -2334,25 +2334,25 @@
         <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
         <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>10</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -2423,25 +2423,25 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>8</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2462,7 +2462,7 @@
         <v>8</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2512,28 +2512,28 @@
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
         <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>6</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2545,13 +2545,13 @@
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2601,25 +2601,25 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
         <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>10</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2690,25 +2690,25 @@
         <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
         <v>8</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2723,10 +2723,10 @@
         <v>6</v>
       </c>
       <c r="AA23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -2779,28 +2779,28 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>6</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -2818,7 +2818,7 @@
         <v>10</v>
       </c>
       <c r="AC24">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2868,28 +2868,28 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
         <v>8</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -2901,10 +2901,10 @@
         <v>8</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC25">
         <v>7</v>
@@ -2957,25 +2957,25 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
         <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
         <v>10</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -2993,7 +2993,7 @@
         <v>9</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC26">
         <v>9</v>
@@ -3046,25 +3046,25 @@
         <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
         <v>6</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>5</v>
@@ -3082,7 +3082,7 @@
         <v>9</v>
       </c>
       <c r="AB27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC27">
         <v>7</v>
@@ -3135,34 +3135,34 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
         <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S28">
         <v>6</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z28">
         <v>8</v>
@@ -3174,7 +3174,7 @@
         <v>9</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3224,25 +3224,25 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
         <v>10</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -3313,25 +3313,25 @@
         <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
         <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>6</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>6</v>
@@ -3352,7 +3352,7 @@
         <v>9</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3402,34 +3402,34 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
         <v>9</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
         <v>10</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z31">
         <v>8</v>
@@ -3441,7 +3441,7 @@
         <v>10</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3491,25 +3491,25 @@
         <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
         <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
         <v>6</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -3518,7 +3518,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z32">
         <v>6</v>
@@ -3580,25 +3580,25 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
         <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
         <v>8</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W33">
         <v>6</v>
@@ -3613,13 +3613,13 @@
         <v>6</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3669,34 +3669,34 @@
         <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
         <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>10</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z34">
         <v>9</v>
@@ -3758,28 +3758,28 @@
         <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
         <v>9</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S35">
         <v>8</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>7</v>
@@ -3794,10 +3794,10 @@
         <v>9</v>
       </c>
       <c r="AB35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC35">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3862,19 +3862,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>65.63</v>
+        <v>71.88</v>
       </c>
       <c r="G2">
-        <v>34.38</v>
+        <v>28.13</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3938,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4002,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4034,7 +4034,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4066,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4691,7 +4691,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4723,16 +4723,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920001</v>
+        <v>20330051920026</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4746,22 +4746,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920002</v>
+        <v>20330051920026</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4769,16 +4769,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920362</v>
+        <v>20330051920001</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4792,16 +4792,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920013</v>
+        <v>20330051920362</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -4815,16 +4815,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920016</v>
+        <v>20330051920013</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -4838,16 +4838,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920363</v>
+        <v>20330051920016</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
@@ -4861,16 +4861,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920021</v>
+        <v>20330051920363</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -4907,22 +4907,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920026</v>
+        <v>20330051920060</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4930,16 +4930,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920028</v>
+        <v>20330051920029</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
@@ -4948,52 +4948,6 @@
         <v>54</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920029</v>
-      </c>
-      <c r="B12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" t="s">
-        <v>140</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920037</v>
-      </c>
-      <c r="B13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>
